--- a/src/components/study/excel/topics/005_002_advanced-power-query-m-code-scripting-and-custom-functions/excel_files/m_code_master.xlsx
+++ b/src/components/study/excel/topics/005_002_advanced-power-query-m-code-scripting-and-custom-functions/excel_files/m_code_master.xlsx
@@ -16,9 +16,9 @@
     <sheet sheetId="10" name="Topic8_Error_Handling" state="visible" r:id="rId13"/>
     <sheet sheetId="11" name="Topic9_Query_Folding_SQL" state="visible" r:id="rId14"/>
     <sheet sheetId="12" name="Topic10_Performance_Optimize" state="visible" r:id="rId15"/>
-    <sheet sheetId="13" name="Topic11_ETL_Query_Architecture" state="visible" r:id="rId16"/>
-    <sheet sheetId="14" name="Topic12_Consolidation_Project" state="visible" r:id="rId17"/>
-    <sheet sheetId="15" name="Topic13_M_Scripting_Challenge" state="visible" r:id="rId18"/>
+    <sheet sheetId="13" name="Topic11_Query_Organize_Docs" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="Topic12_Sales_Pipeline" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="Topic13_ETL_Assessment" state="visible" r:id="rId18"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -5123,7 +5123,7 @@
       <c r="F17"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" algorithmName="SHA-512" hashValue="ufOKo/XcZnBAGM2MfJ2ruA7HD8lV8ljVq6rEHlWr1+9Ka2Bs1Xnmg/a20OZiS6RJly+F9aYwXKEMPF49aKw74w==" saltValue="FmgRjq1+ohuOjGGVWdCGJA==" spinCount="100000"/>
+  <sheetProtection sheet="1" algorithmName="SHA-512" hashValue="+Tox0TrznmqQABwNAVyye4ftQpLGe8ZSU0lqJhV2mWXY2YztI0Eh5EQ+rDqwWhmGEj3CjC5SS/8U+5vb1i+XZA==" saltValue="HGMmqiA7xRdiy2t9IIhk8w==" spinCount="100000"/>
   <mergeCells count="8">
     <mergeCell ref="C1:F2"/>
     <mergeCell ref="C3:F3"/>
